--- a/datasets/output/25136_1000__Dataset4_FirstWithOutl__all_results__20260518_211120.xlsx
+++ b/datasets/output/25136_1000__Dataset4_FirstWithOutl__all_results__20260518_211120.xlsx
@@ -499,22 +499,22 @@
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>931.6993445402627</v>
+        <v>911.45358666725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2183550898438929</v>
+        <v>0.1899084826524112</v>
       </c>
       <c r="H2" t="n">
-        <v>363.895507983053</v>
+        <v>358.0022404272507</v>
       </c>
       <c r="I2" t="n">
-        <v>42.63527069843117</v>
+        <v>39.99282823736</v>
       </c>
       <c r="J2" t="n">
-        <v>54.7621</v>
+        <v>51.8976</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -536,22 +536,22 @@
         <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>927.0088643137129</v>
+        <v>917.3803537464786</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2172558186709754</v>
+        <v>0.1911433709226589</v>
       </c>
       <c r="H3" t="n">
-        <v>356.801131953541</v>
+        <v>354.6139695444955</v>
       </c>
       <c r="I3" t="n">
-        <v>35.90736210310037</v>
+        <v>35.48632412548881</v>
       </c>
       <c r="J3" t="n">
-        <v>54.7621</v>
+        <v>51.8976</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -573,22 +573,22 @@
         <v>39</v>
       </c>
       <c r="F4" t="n">
-        <v>945.0240184879866</v>
+        <v>898.0686871759532</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2214778894831172</v>
+        <v>0.1871196341690324</v>
       </c>
       <c r="H4" t="n">
-        <v>366.8522722657688</v>
+        <v>360.1583555513677</v>
       </c>
       <c r="I4" t="n">
-        <v>42.06905648558437</v>
+        <v>40.55493446292807</v>
       </c>
       <c r="J4" t="n">
-        <v>54.7621</v>
+        <v>51.8976</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -610,22 +610,22 @@
         <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>952.6304593416077</v>
+        <v>971.8264745426349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2232605515464937</v>
+        <v>0.202487645977317</v>
       </c>
       <c r="H5" t="n">
-        <v>369.0839311234571</v>
+        <v>368.1838024227156</v>
       </c>
       <c r="I5" t="n">
-        <v>32.30917393086187</v>
+        <v>31.97008142623586</v>
       </c>
       <c r="J5" t="n">
-        <v>54.7621</v>
+        <v>51.8976</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -647,22 +647,22 @@
         <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>1024.439207872937</v>
+        <v>1106.531136622008</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2400898064225643</v>
+        <v>0.2305544157568284</v>
       </c>
       <c r="H6" t="n">
-        <v>406.0866684404033</v>
+        <v>410.7854705341828</v>
       </c>
       <c r="I6" t="n">
-        <v>29.88173333244081</v>
+        <v>30.43569527772248</v>
       </c>
       <c r="J6" t="n">
-        <v>54.7621</v>
+        <v>51.8976</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -684,22 +684,22 @@
         <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>991.3162015086775</v>
+        <v>937.2592520195419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2323270264303377</v>
+        <v>0.1952852948374499</v>
       </c>
       <c r="H7" t="n">
-        <v>396.541149421471</v>
+        <v>394.082612505031</v>
       </c>
       <c r="I7" t="n">
-        <v>51.48666210654655</v>
+        <v>48.845128392262</v>
       </c>
       <c r="J7" t="n">
-        <v>54.7621</v>
+        <v>51.8976</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -721,22 +721,22 @@
         <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>890.7501472348176</v>
+        <v>941.2836092136708</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2019260256346708</v>
+        <v>0.2006518399483596</v>
       </c>
       <c r="H8" t="n">
-        <v>368.8917097269101</v>
+        <v>360.9998455730934</v>
       </c>
       <c r="I8" t="n">
-        <v>39.93153341303213</v>
+        <v>38.74921780138439</v>
       </c>
       <c r="J8" t="n">
-        <v>53.0712</v>
+        <v>52.6571</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -758,22 +758,22 @@
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>894.7138754501345</v>
+        <v>927.7350823657914</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2028245715262427</v>
+        <v>0.1977637233233525</v>
       </c>
       <c r="H9" t="n">
-        <v>364.316499888521</v>
+        <v>354.6361719555617</v>
       </c>
       <c r="I9" t="n">
-        <v>34.18095596157157</v>
+        <v>34.39225745897289</v>
       </c>
       <c r="J9" t="n">
-        <v>53.0712</v>
+        <v>52.6571</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -795,22 +795,22 @@
         <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>895.6290141523416</v>
+        <v>919.890748385193</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2030320262447345</v>
+        <v>0.1960915598744517</v>
       </c>
       <c r="H10" t="n">
-        <v>372.5863065576249</v>
+        <v>364.8789278180855</v>
       </c>
       <c r="I10" t="n">
-        <v>39.77962682989394</v>
+        <v>39.24584462834877</v>
       </c>
       <c r="J10" t="n">
-        <v>53.0712</v>
+        <v>52.6571</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -832,22 +832,22 @@
         <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>933.0794771448927</v>
+        <v>1001.358560078251</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2115217505223446</v>
+        <v>0.2134579159362917</v>
       </c>
       <c r="H11" t="n">
-        <v>378.7068481636584</v>
+        <v>368.9586440892642</v>
       </c>
       <c r="I11" t="n">
-        <v>30.95773847119865</v>
+        <v>31.20628104600622</v>
       </c>
       <c r="J11" t="n">
-        <v>53.0712</v>
+        <v>52.6571</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -869,22 +869,22 @@
         <v>39</v>
       </c>
       <c r="F12" t="n">
-        <v>1012.065699681971</v>
+        <v>1136.518443707013</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2294273035512383</v>
+        <v>0.2422697204464891</v>
       </c>
       <c r="H12" t="n">
-        <v>412.2207091643496</v>
+        <v>410.156705411405</v>
       </c>
       <c r="I12" t="n">
-        <v>29.10356661655717</v>
+        <v>29.78010843911064</v>
       </c>
       <c r="J12" t="n">
-        <v>53.0712</v>
+        <v>52.6571</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -906,22 +906,22 @@
         <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>949.3877777761636</v>
+        <v>944.7429359577334</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2152187135164577</v>
+        <v>0.20138925879788</v>
       </c>
       <c r="H13" t="n">
-        <v>406.8191369455191</v>
+        <v>401.0166392521221</v>
       </c>
       <c r="I13" t="n">
-        <v>48.15999922199502</v>
+        <v>47.25372073781973</v>
       </c>
       <c r="J13" t="n">
-        <v>53.0712</v>
+        <v>52.6571</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -943,22 +943,22 @@
         <v>39</v>
       </c>
       <c r="F14" t="n">
-        <v>929.376387739871</v>
+        <v>966.4252925142971</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2096916406663438</v>
+        <v>0.2057750730686533</v>
       </c>
       <c r="H14" t="n">
-        <v>370.5520581043276</v>
+        <v>375.3518228518952</v>
       </c>
       <c r="I14" t="n">
-        <v>40.27107426298211</v>
+        <v>39.84675176443786</v>
       </c>
       <c r="J14" t="n">
-        <v>52.6453</v>
+        <v>52.5123</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -980,22 +980,22 @@
         <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>925.8231981977387</v>
+        <v>969.7730954378493</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2088899480964474</v>
+        <v>0.2064879004300121</v>
       </c>
       <c r="H15" t="n">
-        <v>366.1966336045975</v>
+        <v>371.3588185733934</v>
       </c>
       <c r="I15" t="n">
-        <v>34.35425641897048</v>
+        <v>35.28757221517149</v>
       </c>
       <c r="J15" t="n">
-        <v>52.6453</v>
+        <v>52.5123</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1017,22 +1017,22 @@
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>946.5018776560763</v>
+        <v>953.2966323263433</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2135555994726107</v>
+        <v>0.2029796671222286</v>
       </c>
       <c r="H16" t="n">
-        <v>373.7399357863218</v>
+        <v>378.64964191917</v>
       </c>
       <c r="I16" t="n">
-        <v>39.98258834222523</v>
+        <v>40.13026183676185</v>
       </c>
       <c r="J16" t="n">
-        <v>52.6453</v>
+        <v>52.5123</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1054,22 +1054,22 @@
         <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>947.5487869465961</v>
+        <v>1016.351596094246</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2137918096127153</v>
+        <v>0.2164055779269061</v>
       </c>
       <c r="H17" t="n">
-        <v>377.308164001689</v>
+        <v>381.2412632672772</v>
       </c>
       <c r="I17" t="n">
-        <v>30.7151399564924</v>
+        <v>31.68175856088231</v>
       </c>
       <c r="J17" t="n">
-        <v>52.6453</v>
+        <v>52.5123</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1091,22 +1091,22 @@
         <v>39</v>
       </c>
       <c r="F18" t="n">
-        <v>1015.590379035486</v>
+        <v>1125.973661701304</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2291437738619544</v>
+        <v>0.2397467391474931</v>
       </c>
       <c r="H18" t="n">
-        <v>408.5111512133818</v>
+        <v>415.7818656890346</v>
       </c>
       <c r="I18" t="n">
-        <v>28.84723019655756</v>
+        <v>30.02044126462734</v>
       </c>
       <c r="J18" t="n">
-        <v>52.6453</v>
+        <v>52.5123</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1128,22 +1128,22 @@
         <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>1025.923225911341</v>
+        <v>985.4607844182073</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2314751345923698</v>
+        <v>0.2098281848484931</v>
       </c>
       <c r="H19" t="n">
-        <v>410.774212584872</v>
+        <v>412.8267482095361</v>
       </c>
       <c r="I19" t="n">
-        <v>48.586483073979</v>
+        <v>48.12528660857132</v>
       </c>
       <c r="J19" t="n">
-        <v>52.6453</v>
+        <v>52.5123</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1165,22 +1165,22 @@
         <v>39</v>
       </c>
       <c r="F20" t="n">
-        <v>926.382151494112</v>
+        <v>995.6203806038152</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2075063023021183</v>
+        <v>0.2073011130617497</v>
       </c>
       <c r="H20" t="n">
-        <v>373.3780049483186</v>
+        <v>388.0217866831319</v>
       </c>
       <c r="I20" t="n">
-        <v>38.70794726400098</v>
+        <v>40.33406985350344</v>
       </c>
       <c r="J20" t="n">
-        <v>51.2523</v>
+        <v>50.1946</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1202,22 +1202,22 @@
         <v>39</v>
       </c>
       <c r="F21" t="n">
-        <v>926.3349458702158</v>
+        <v>951.2046489247601</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2074957284105048</v>
+        <v>0.1980531800203066</v>
       </c>
       <c r="H21" t="n">
-        <v>371.6319310242985</v>
+        <v>375.359783915047</v>
       </c>
       <c r="I21" t="n">
-        <v>35.57422040973976</v>
+        <v>36.45051757399121</v>
       </c>
       <c r="J21" t="n">
-        <v>51.2523</v>
+        <v>50.1946</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1239,22 +1239,22 @@
         <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>924.5249793863259</v>
+        <v>933.6637698644223</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2070903023649392</v>
+        <v>0.1944009408495051</v>
       </c>
       <c r="H22" t="n">
-        <v>379.2359445830443</v>
+        <v>382.4358962002007</v>
       </c>
       <c r="I22" t="n">
-        <v>39.65435498265661</v>
+        <v>40.73938635106165</v>
       </c>
       <c r="J22" t="n">
-        <v>51.2523</v>
+        <v>50.1946</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1276,22 +1276,22 @@
         <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>952.6000171761234</v>
+        <v>993.5451648008944</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2133790108308321</v>
+        <v>0.2068690261396962</v>
       </c>
       <c r="H23" t="n">
-        <v>377.8515979951146</v>
+        <v>382.6668480432159</v>
       </c>
       <c r="I23" t="n">
-        <v>31.94954211485631</v>
+        <v>32.79298458648993</v>
       </c>
       <c r="J23" t="n">
-        <v>51.2523</v>
+        <v>50.1946</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -1313,22 +1313,22 @@
         <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>1016.29182153475</v>
+        <v>1079.663745222108</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2276457481466282</v>
+        <v>0.224800034709236</v>
       </c>
       <c r="H24" t="n">
-        <v>404.2041024795543</v>
+        <v>410.2629896769246</v>
       </c>
       <c r="I24" t="n">
-        <v>29.68966457278483</v>
+        <v>30.26204662849893</v>
       </c>
       <c r="J24" t="n">
-        <v>51.2523</v>
+        <v>50.1946</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -1350,22 +1350,22 @@
         <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>975.3461307245094</v>
+        <v>964.751057236404</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2184740592474679</v>
+        <v>0.2008737184260086</v>
       </c>
       <c r="H25" t="n">
-        <v>409.2154520543064</v>
+        <v>411.6272414854519</v>
       </c>
       <c r="I25" t="n">
-        <v>46.2975490558466</v>
+        <v>47.06501811533164</v>
       </c>
       <c r="J25" t="n">
-        <v>51.2523</v>
+        <v>50.1946</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1387,22 +1387,22 @@
         <v>39</v>
       </c>
       <c r="F26" t="n">
-        <v>993.0586237999836</v>
+        <v>1048.899799755236</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2235349427159961</v>
+        <v>0.221882189533556</v>
       </c>
       <c r="H26" t="n">
-        <v>387.1405359228107</v>
+        <v>398.8979484291079</v>
       </c>
       <c r="I26" t="n">
-        <v>38.39895256121369</v>
+        <v>40.01121134536763</v>
       </c>
       <c r="J26" t="n">
-        <v>48.7691</v>
+        <v>46.8595</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -1424,22 +1424,22 @@
         <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>960.7750349445483</v>
+        <v>972.7808493861922</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2162679898770467</v>
+        <v>0.2057801372909865</v>
       </c>
       <c r="H27" t="n">
-        <v>386.0842694454429</v>
+        <v>388.7641896085395</v>
       </c>
       <c r="I27" t="n">
-        <v>37.78542940859298</v>
+        <v>39.46566638364834</v>
       </c>
       <c r="J27" t="n">
-        <v>48.7691</v>
+        <v>46.8595</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1461,22 +1461,22 @@
         <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>951.8369526854326</v>
+        <v>969.5390505460264</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2142560505434583</v>
+        <v>0.2050943735747085</v>
       </c>
       <c r="H28" t="n">
-        <v>389.599507353668</v>
+        <v>393.9568371841468</v>
       </c>
       <c r="I28" t="n">
-        <v>40.16095613767948</v>
+        <v>42.08779460352753</v>
       </c>
       <c r="J28" t="n">
-        <v>48.7691</v>
+        <v>46.8595</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -1498,22 +1498,22 @@
         <v>39</v>
       </c>
       <c r="F29" t="n">
-        <v>987.1129272542463</v>
+        <v>994.5325380588208</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2221965817120179</v>
+        <v>0.2103814465007521</v>
       </c>
       <c r="H29" t="n">
-        <v>387.946425015012</v>
+        <v>387.5582301804278</v>
       </c>
       <c r="I29" t="n">
-        <v>34.72843463402711</v>
+        <v>35.73038588290922</v>
       </c>
       <c r="J29" t="n">
-        <v>48.7691</v>
+        <v>46.8595</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1535,22 +1535,22 @@
         <v>39</v>
       </c>
       <c r="F30" t="n">
-        <v>1030.32141926743</v>
+        <v>1060.890837927159</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2319227021600258</v>
+        <v>0.2244187500372263</v>
       </c>
       <c r="H30" t="n">
-        <v>401.8943814473539</v>
+        <v>402.3435303414147</v>
       </c>
       <c r="I30" t="n">
-        <v>31.07497645430217</v>
+        <v>31.96223745556775</v>
       </c>
       <c r="J30" t="n">
-        <v>48.7691</v>
+        <v>46.8595</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -1572,22 +1572,22 @@
         <v>39</v>
       </c>
       <c r="F31" t="n">
-        <v>970.1638126091308</v>
+        <v>975.5133008132369</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2183813795875099</v>
+        <v>0.2063581546626823</v>
       </c>
       <c r="H31" t="n">
-        <v>405.5489866644969</v>
+        <v>408.6156668848034</v>
       </c>
       <c r="I31" t="n">
-        <v>44.13008761626057</v>
+        <v>46.04325900430232</v>
       </c>
       <c r="J31" t="n">
-        <v>48.7691</v>
+        <v>46.8595</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -1609,22 +1609,22 @@
         <v>39</v>
       </c>
       <c r="F32" t="n">
-        <v>1034.062415927551</v>
+        <v>1095.319011842485</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2359818976087292</v>
+        <v>0.2327312167264722</v>
       </c>
       <c r="H32" t="n">
-        <v>397.7725539110826</v>
+        <v>411.3608734194689</v>
       </c>
       <c r="I32" t="n">
-        <v>40.76315028535679</v>
+        <v>40.01732001116755</v>
       </c>
       <c r="J32" t="n">
-        <v>46.1348</v>
+        <v>44.9507</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1646,22 +1646,22 @@
         <v>39</v>
       </c>
       <c r="F33" t="n">
-        <v>1029.073699215815</v>
+        <v>1017.144552690353</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2348434297385747</v>
+        <v>0.2161208623012301</v>
       </c>
       <c r="H33" t="n">
-        <v>402.6637768981251</v>
+        <v>405.6300273953582</v>
       </c>
       <c r="I33" t="n">
-        <v>41.45198291030034</v>
+        <v>40.61577568458971</v>
       </c>
       <c r="J33" t="n">
-        <v>46.1348</v>
+        <v>44.9507</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1683,22 +1683,22 @@
         <v>39</v>
       </c>
       <c r="F34" t="n">
-        <v>1020.876062870219</v>
+        <v>1021.604854819181</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2329726589311814</v>
+        <v>0.217068578473584</v>
       </c>
       <c r="H34" t="n">
-        <v>405.0499455983104</v>
+        <v>409.1744063430083</v>
       </c>
       <c r="I34" t="n">
-        <v>42.6832607331927</v>
+        <v>42.40398021463029</v>
       </c>
       <c r="J34" t="n">
-        <v>46.1348</v>
+        <v>44.9507</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -1720,22 +1720,22 @@
         <v>39</v>
       </c>
       <c r="F35" t="n">
-        <v>1045.359422408908</v>
+        <v>1023.205564262941</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2385599712198636</v>
+        <v>0.2174086940494518</v>
       </c>
       <c r="H35" t="n">
-        <v>400.9544769081361</v>
+        <v>402.3522963017776</v>
       </c>
       <c r="I35" t="n">
-        <v>38.22224663297447</v>
+        <v>37.43647311388232</v>
       </c>
       <c r="J35" t="n">
-        <v>46.1348</v>
+        <v>44.9507</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -1757,22 +1757,22 @@
         <v>39</v>
       </c>
       <c r="F36" t="n">
-        <v>1071.817104518365</v>
+        <v>1065.276430785528</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2445978408245893</v>
+        <v>0.2263478285378311</v>
       </c>
       <c r="H36" t="n">
-        <v>407.2213287959084</v>
+        <v>407.8743599379638</v>
       </c>
       <c r="I36" t="n">
-        <v>33.83059683467522</v>
+        <v>32.92968221582176</v>
       </c>
       <c r="J36" t="n">
-        <v>46.1348</v>
+        <v>44.9507</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
@@ -1794,22 +1794,22 @@
         <v>39</v>
       </c>
       <c r="F37" t="n">
-        <v>995.9465605220825</v>
+        <v>1016.526126604293</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2272835330332271</v>
+        <v>0.2159894603499191</v>
       </c>
       <c r="H37" t="n">
-        <v>411.580708140128</v>
+        <v>418.6433582700762</v>
       </c>
       <c r="I37" t="n">
-        <v>45.18461401581128</v>
+        <v>45.16727462841269</v>
       </c>
       <c r="J37" t="n">
-        <v>46.1348</v>
+        <v>44.9507</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -1831,22 +1831,22 @@
         <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>1095.315474982411</v>
+        <v>1163.45447284098</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2452163571935448</v>
+        <v>0.2471610417807384</v>
       </c>
       <c r="H38" t="n">
-        <v>413.9724633267393</v>
+        <v>427.1518433933658</v>
       </c>
       <c r="I38" t="n">
-        <v>41.37805315211672</v>
+        <v>40.03979843335182</v>
       </c>
       <c r="J38" t="n">
-        <v>44.0625</v>
+        <v>43.7943</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
@@ -1868,22 +1868,22 @@
         <v>39</v>
       </c>
       <c r="F39" t="n">
-        <v>1078.982532678379</v>
+        <v>1104.205889156193</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2415597808869687</v>
+        <v>0.2345744369677396</v>
       </c>
       <c r="H39" t="n">
-        <v>419.9587420410392</v>
+        <v>426.6631981801534</v>
       </c>
       <c r="I39" t="n">
-        <v>42.77560782042248</v>
+        <v>41.05033466739467</v>
       </c>
       <c r="J39" t="n">
-        <v>44.0625</v>
+        <v>43.7943</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -1905,22 +1905,22 @@
         <v>39</v>
       </c>
       <c r="F40" t="n">
-        <v>1089.473725762265</v>
+        <v>1107.842722320316</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2439085216921562</v>
+        <v>0.2353470357196552</v>
       </c>
       <c r="H40" t="n">
-        <v>423.7970749644293</v>
+        <v>428.677695048059</v>
       </c>
       <c r="I40" t="n">
-        <v>43.25913680525539</v>
+        <v>42.16329278056362</v>
       </c>
       <c r="J40" t="n">
-        <v>44.0625</v>
+        <v>43.7943</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1942,22 +1942,22 @@
         <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>1069.52891392017</v>
+        <v>1106.309447152638</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2394433295018353</v>
+        <v>0.2350213109950302</v>
       </c>
       <c r="H41" t="n">
-        <v>414.5997345702895</v>
+        <v>421.3422807609036</v>
       </c>
       <c r="I41" t="n">
-        <v>40.41044149002528</v>
+        <v>38.62693526937144</v>
       </c>
       <c r="J41" t="n">
-        <v>44.0625</v>
+        <v>43.7943</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1979,22 +1979,22 @@
         <v>39</v>
       </c>
       <c r="F42" t="n">
-        <v>1072.441227584961</v>
+        <v>1128.366591247574</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2400953306505421</v>
+        <v>0.2397070695188684</v>
       </c>
       <c r="H42" t="n">
-        <v>414.1898414282198</v>
+        <v>420.3687354423203</v>
       </c>
       <c r="I42" t="n">
-        <v>35.79175475292063</v>
+        <v>33.7798184666156</v>
       </c>
       <c r="J42" t="n">
-        <v>44.0625</v>
+        <v>43.7943</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -2016,22 +2016,22 @@
         <v>39</v>
       </c>
       <c r="F43" t="n">
-        <v>1082.982830347899</v>
+        <v>1103.646555584781</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2424553570425281</v>
+        <v>0.2344556136949428</v>
       </c>
       <c r="H43" t="n">
-        <v>425.1570956356856</v>
+        <v>431.525558768052</v>
       </c>
       <c r="I43" t="n">
-        <v>44.81621053912701</v>
+        <v>44.11446276545571</v>
       </c>
       <c r="J43" t="n">
-        <v>44.0625</v>
+        <v>43.7943</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -2053,22 +2053,22 @@
         <v>39</v>
       </c>
       <c r="F44" t="n">
-        <v>1154.854395755438</v>
+        <v>1211.290259339101</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2549627342809452</v>
+        <v>0.2566835097342733</v>
       </c>
       <c r="H44" t="n">
-        <v>426.2460280450314</v>
+        <v>440.6277103651444</v>
       </c>
       <c r="I44" t="n">
-        <v>41.47416269955709</v>
+        <v>41.18634735985805</v>
       </c>
       <c r="J44" t="n">
-        <v>42.4358</v>
+        <v>42.0785</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -2090,22 +2090,22 @@
         <v>39</v>
       </c>
       <c r="F45" t="n">
-        <v>1113.637799433237</v>
+        <v>1161.433408672051</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2458631489698566</v>
+        <v>0.2461183860450113</v>
       </c>
       <c r="H45" t="n">
-        <v>436.486027930495</v>
+        <v>446.3773242232429</v>
       </c>
       <c r="I45" t="n">
-        <v>42.94452072334246</v>
+        <v>42.44058528485927</v>
       </c>
       <c r="J45" t="n">
-        <v>42.4358</v>
+        <v>42.0785</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -2127,22 +2127,22 @@
         <v>39</v>
       </c>
       <c r="F46" t="n">
-        <v>1122.946773843669</v>
+        <v>1159.167401786951</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2479183358209076</v>
+        <v>0.2456381984137932</v>
       </c>
       <c r="H46" t="n">
-        <v>439.0063467735617</v>
+        <v>446.6027217866863</v>
       </c>
       <c r="I46" t="n">
-        <v>43.03000176916044</v>
+        <v>42.95187746871333</v>
       </c>
       <c r="J46" t="n">
-        <v>42.4358</v>
+        <v>42.0785</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -2164,22 +2164,22 @@
         <v>39</v>
       </c>
       <c r="F47" t="n">
-        <v>1103.566669835123</v>
+        <v>1150.166808830744</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2436396974688964</v>
+        <v>0.2437308902588103</v>
       </c>
       <c r="H47" t="n">
-        <v>430.4800235451269</v>
+        <v>441.3181872010514</v>
       </c>
       <c r="I47" t="n">
-        <v>41.77868831558187</v>
+        <v>40.5438597593736</v>
       </c>
       <c r="J47" t="n">
-        <v>42.4358</v>
+        <v>42.0785</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
@@ -2201,22 +2201,22 @@
         <v>39</v>
       </c>
       <c r="F48" t="n">
-        <v>1111.672784895363</v>
+        <v>1153.10233319295</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2454293233020326</v>
+        <v>0.2443529547808289</v>
       </c>
       <c r="H48" t="n">
-        <v>424.5812273792632</v>
+        <v>434.566656646086</v>
       </c>
       <c r="I48" t="n">
-        <v>37.29271745470578</v>
+        <v>36.31848654989507</v>
       </c>
       <c r="J48" t="n">
-        <v>42.4358</v>
+        <v>42.0785</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
@@ -2238,22 +2238,22 @@
         <v>39</v>
       </c>
       <c r="F49" t="n">
-        <v>1123.780430965118</v>
+        <v>1176.576667000465</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2481023862950787</v>
+        <v>0.2493273813015824</v>
       </c>
       <c r="H49" t="n">
-        <v>442.3573685167837</v>
+        <v>449.5647567227776</v>
       </c>
       <c r="I49" t="n">
-        <v>44.25794680583704</v>
+        <v>44.22494504853808</v>
       </c>
       <c r="J49" t="n">
-        <v>42.4358</v>
+        <v>42.0785</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
@@ -2275,22 +2275,22 @@
         <v>39</v>
       </c>
       <c r="F50" t="n">
-        <v>1217.473787321451</v>
+        <v>1212.346337080013</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2672660177582066</v>
+        <v>0.2586923430108763</v>
       </c>
       <c r="H50" t="n">
-        <v>440.2181594103697</v>
+        <v>442.9038011774535</v>
       </c>
       <c r="I50" t="n">
-        <v>42.59294440267259</v>
+        <v>40.65995516219013</v>
       </c>
       <c r="J50" t="n">
-        <v>40.7386</v>
+        <v>40.0519</v>
       </c>
       <c r="K50" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
@@ -2312,22 +2312,22 @@
         <v>39</v>
       </c>
       <c r="F51" t="n">
-        <v>1236.850645006569</v>
+        <v>1177.993597121583</v>
       </c>
       <c r="G51" t="n">
-        <v>0.271519723787938</v>
+        <v>0.2513621020418693</v>
       </c>
       <c r="H51" t="n">
-        <v>460.0962066160161</v>
+        <v>455.1853698492327</v>
       </c>
       <c r="I51" t="n">
-        <v>44.38014557263361</v>
+        <v>42.96714433940822</v>
       </c>
       <c r="J51" t="n">
-        <v>40.7386</v>
+        <v>40.0519</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
@@ -2349,22 +2349,22 @@
         <v>39</v>
       </c>
       <c r="F52" t="n">
-        <v>1238.70796308232</v>
+        <v>1182.35276280956</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2719274516675734</v>
+        <v>0.2522922675819505</v>
       </c>
       <c r="H52" t="n">
-        <v>461.4964873681139</v>
+        <v>457.1675899215061</v>
       </c>
       <c r="I52" t="n">
-        <v>44.43474784725284</v>
+        <v>43.35291928990795</v>
       </c>
       <c r="J52" t="n">
-        <v>40.7386</v>
+        <v>40.0519</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -2386,22 +2386,22 @@
         <v>39</v>
       </c>
       <c r="F53" t="n">
-        <v>1224.218880994003</v>
+        <v>1176.17182976004</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2687467349153581</v>
+        <v>0.2509733704948154</v>
       </c>
       <c r="H53" t="n">
-        <v>455.4764496522939</v>
+        <v>450.2375087091166</v>
       </c>
       <c r="I53" t="n">
-        <v>43.41125891833207</v>
+        <v>41.88762574243506</v>
       </c>
       <c r="J53" t="n">
-        <v>40.7386</v>
+        <v>40.0519</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
@@ -2423,22 +2423,22 @@
         <v>39</v>
       </c>
       <c r="F54" t="n">
-        <v>1212.530522160496</v>
+        <v>1172.802959069906</v>
       </c>
       <c r="G54" t="n">
-        <v>0.266180847130264</v>
+        <v>0.2502545156383471</v>
       </c>
       <c r="H54" t="n">
-        <v>445.9838266846474</v>
+        <v>442.8013820745767</v>
       </c>
       <c r="I54" t="n">
-        <v>39.47369235414236</v>
+        <v>38.14369112918217</v>
       </c>
       <c r="J54" t="n">
-        <v>40.7386</v>
+        <v>40.0519</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -2460,22 +2460,22 @@
         <v>39</v>
       </c>
       <c r="F55" t="n">
-        <v>1233.161836341816</v>
+        <v>1182.389029049962</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2707099378094903</v>
+        <v>0.252300006128614</v>
       </c>
       <c r="H55" t="n">
-        <v>462.4816076760527</v>
+        <v>455.7445989244708</v>
       </c>
       <c r="I55" t="n">
-        <v>45.05879081614314</v>
+        <v>43.8149409503841</v>
       </c>
       <c r="J55" t="n">
-        <v>40.7386</v>
+        <v>40.0519</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
@@ -2497,22 +2497,22 @@
         <v>39</v>
       </c>
       <c r="F56" t="n">
-        <v>1240.947671237788</v>
+        <v>1271.604193939281</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2703157952999471</v>
+        <v>0.2730805416128783</v>
       </c>
       <c r="H56" t="n">
-        <v>451.010137788531</v>
+        <v>455.8676527562059</v>
       </c>
       <c r="I56" t="n">
-        <v>42.99533958941923</v>
+        <v>41.29139598067135</v>
       </c>
       <c r="J56" t="n">
-        <v>38.2162</v>
+        <v>38.2767</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -2534,22 +2534,22 @@
         <v>39</v>
       </c>
       <c r="F57" t="n">
-        <v>1335.065791753793</v>
+        <v>1310.640135836771</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2908175579359519</v>
+        <v>0.281463618836548</v>
       </c>
       <c r="H57" t="n">
-        <v>478.4522503850968</v>
+        <v>478.7513664436177</v>
       </c>
       <c r="I57" t="n">
-        <v>44.87621957606953</v>
+        <v>43.2248502775126</v>
       </c>
       <c r="J57" t="n">
-        <v>38.2162</v>
+        <v>38.2767</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -2571,22 +2571,22 @@
         <v>39</v>
       </c>
       <c r="F58" t="n">
-        <v>1322.790757554067</v>
+        <v>1312.720389585183</v>
       </c>
       <c r="G58" t="n">
-        <v>0.288143685613259</v>
+        <v>0.2819103591217848</v>
       </c>
       <c r="H58" t="n">
-        <v>478.2674265364102</v>
+        <v>478.5994359586026</v>
       </c>
       <c r="I58" t="n">
-        <v>44.86377466373622</v>
+        <v>43.19238636262988</v>
       </c>
       <c r="J58" t="n">
-        <v>38.2162</v>
+        <v>38.2767</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
@@ -2608,22 +2608,22 @@
         <v>39</v>
       </c>
       <c r="F59" t="n">
-        <v>1315.746014925171</v>
+        <v>1307.559331675859</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2866091283949727</v>
+        <v>0.2808020075640508</v>
       </c>
       <c r="H59" t="n">
-        <v>475.2062143922331</v>
+        <v>477.3324564502865</v>
       </c>
       <c r="I59" t="n">
-        <v>44.25832580042199</v>
+        <v>42.70506737379337</v>
       </c>
       <c r="J59" t="n">
-        <v>38.2162</v>
+        <v>38.2767</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -2645,22 +2645,22 @@
         <v>39</v>
       </c>
       <c r="F60" t="n">
-        <v>1307.763866981992</v>
+        <v>1276.322720334673</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2848703760531354</v>
+        <v>0.2740938582957028</v>
       </c>
       <c r="H60" t="n">
-        <v>466.5241102064983</v>
+        <v>467.1404311813891</v>
       </c>
       <c r="I60" t="n">
-        <v>41.66553296938314</v>
+        <v>39.89026263020456</v>
       </c>
       <c r="J60" t="n">
-        <v>38.2162</v>
+        <v>38.2767</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
@@ -2682,22 +2682,22 @@
         <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>1315.550212191125</v>
+        <v>1310.989217729918</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2865664766595271</v>
+        <v>0.28153858514517</v>
       </c>
       <c r="H61" t="n">
-        <v>476.8278172634225</v>
+        <v>477.0229006262965</v>
       </c>
       <c r="I61" t="n">
-        <v>45.13483059270117</v>
+        <v>43.45273658980487</v>
       </c>
       <c r="J61" t="n">
-        <v>38.2162</v>
+        <v>38.2767</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
@@ -2719,22 +2719,22 @@
         <v>39</v>
       </c>
       <c r="F62" t="n">
-        <v>1320.191078657883</v>
+        <v>1326.111233693992</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2844392941454333</v>
+        <v>0.2841444268484882</v>
       </c>
       <c r="H62" t="n">
-        <v>463.5016430032535</v>
+        <v>469.3672348304589</v>
       </c>
       <c r="I62" t="n">
-        <v>43.83412622133155</v>
+        <v>42.36563323156238</v>
       </c>
       <c r="J62" t="n">
-        <v>36.2965</v>
+        <v>36.2506</v>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -2756,22 +2756,22 @@
         <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>1457.560686886686</v>
+        <v>1387.943278461921</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3140360055861421</v>
+        <v>0.2973931125356705</v>
       </c>
       <c r="H63" t="n">
-        <v>500.4084821540113</v>
+        <v>497.4257969176733</v>
       </c>
       <c r="I63" t="n">
-        <v>46.10643818470751</v>
+        <v>44.23256000339743</v>
       </c>
       <c r="J63" t="n">
-        <v>36.2965</v>
+        <v>36.2506</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
@@ -2793,22 +2793,22 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>1457.08084361355</v>
+        <v>1444.432433770371</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3139326218531979</v>
+        <v>0.3094969830485256</v>
       </c>
       <c r="H64" t="n">
-        <v>501.7044055834998</v>
+        <v>498.8678620994361</v>
       </c>
       <c r="I64" t="n">
-        <v>46.16537160276506</v>
+        <v>44.27145594965031</v>
       </c>
       <c r="J64" t="n">
-        <v>36.2965</v>
+        <v>36.2506</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
@@ -2830,22 +2830,22 @@
         <v>39</v>
       </c>
       <c r="F65" t="n">
-        <v>1457.045741640808</v>
+        <v>1387.210030401309</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3139250590234597</v>
+        <v>0.2972360002628637</v>
       </c>
       <c r="H65" t="n">
-        <v>499.1770716709106</v>
+        <v>496.8343058356871</v>
       </c>
       <c r="I65" t="n">
-        <v>45.51234800287174</v>
+        <v>43.90179481114296</v>
       </c>
       <c r="J65" t="n">
-        <v>36.2965</v>
+        <v>36.2506</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
@@ -2867,22 +2867,22 @@
         <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>1448.071216885735</v>
+        <v>1377.371488620749</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3119914696151607</v>
+        <v>0.2951279065040355</v>
       </c>
       <c r="H66" t="n">
-        <v>492.6822965635417</v>
+        <v>490.1403841580163</v>
       </c>
       <c r="I66" t="n">
-        <v>43.83296862204995</v>
+        <v>42.25802485003002</v>
       </c>
       <c r="J66" t="n">
-        <v>36.2965</v>
+        <v>36.2506</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
@@ -2904,22 +2904,22 @@
         <v>39</v>
       </c>
       <c r="F67" t="n">
-        <v>1506.178192022911</v>
+        <v>1433.409747349368</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3245107990214365</v>
+        <v>0.3071351638919967</v>
       </c>
       <c r="H67" t="n">
-        <v>504.5885704344886</v>
+        <v>496.8381620200482</v>
       </c>
       <c r="I67" t="n">
-        <v>46.22394597728083</v>
+        <v>44.3397336242087</v>
       </c>
       <c r="J67" t="n">
-        <v>36.2965</v>
+        <v>36.2506</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
@@ -2941,22 +2941,22 @@
         <v>39</v>
       </c>
       <c r="F68" t="n">
-        <v>1333.512746171964</v>
+        <v>1364.151369378447</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2881828113813041</v>
+        <v>0.2925700249141471</v>
       </c>
       <c r="H68" t="n">
-        <v>471.3418972419283</v>
+        <v>479.5942764040804</v>
       </c>
       <c r="I68" t="n">
-        <v>43.78154736476109</v>
+        <v>43.53174633996164</v>
       </c>
       <c r="J68" t="n">
-        <v>33.2895</v>
+        <v>33.4629</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
@@ -2978,22 +2978,22 @@
         <v>39</v>
       </c>
       <c r="F69" t="n">
-        <v>1486.935242593832</v>
+        <v>1623.158586423865</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3213386447056676</v>
+        <v>0.3481193940273773</v>
       </c>
       <c r="H69" t="n">
-        <v>515.3388361860848</v>
+        <v>531.7660652649612</v>
       </c>
       <c r="I69" t="n">
-        <v>45.84714542637307</v>
+        <v>45.89792581541313</v>
       </c>
       <c r="J69" t="n">
-        <v>33.2895</v>
+        <v>33.4629</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
@@ -3015,22 +3015,22 @@
         <v>39</v>
       </c>
       <c r="F70" t="n">
-        <v>1480.628992888866</v>
+        <v>1624.971290251741</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3199758135107902</v>
+        <v>0.3485081652561342</v>
       </c>
       <c r="H70" t="n">
-        <v>513.3449729173994</v>
+        <v>531.7163438118139</v>
       </c>
       <c r="I70" t="n">
-        <v>45.83914334313152</v>
+        <v>45.7705241282462</v>
       </c>
       <c r="J70" t="n">
-        <v>33.2895</v>
+        <v>33.4629</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
@@ -3052,22 +3052,22 @@
         <v>39</v>
       </c>
       <c r="F71" t="n">
-        <v>1470.936869311175</v>
+        <v>1615.897655206262</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3178812677864303</v>
+        <v>0.3465621395504039</v>
       </c>
       <c r="H71" t="n">
-        <v>512.0650443889963</v>
+        <v>529.6668576844456</v>
       </c>
       <c r="I71" t="n">
-        <v>45.74251982428434</v>
+        <v>45.64780967408016</v>
       </c>
       <c r="J71" t="n">
-        <v>33.2895</v>
+        <v>33.4629</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
@@ -3089,22 +3089,22 @@
         <v>39</v>
       </c>
       <c r="F72" t="n">
-        <v>1460.700108670936</v>
+        <v>1604.188689226859</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3156690216198975</v>
+        <v>0.3440509134905907</v>
       </c>
       <c r="H72" t="n">
-        <v>505.8199439678003</v>
+        <v>522.7709598644719</v>
       </c>
       <c r="I72" t="n">
-        <v>44.64305844704885</v>
+        <v>44.26454564237328</v>
       </c>
       <c r="J72" t="n">
-        <v>33.2895</v>
+        <v>33.4629</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
@@ -3126,22 +3126,22 @@
         <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>1465.255295576877</v>
+        <v>1587.653107067666</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3166534340844124</v>
+        <v>0.3405045213578106</v>
       </c>
       <c r="H73" t="n">
-        <v>511.355570506369</v>
+        <v>526.7560455201386</v>
       </c>
       <c r="I73" t="n">
-        <v>45.58233325197892</v>
+        <v>45.9045082359101</v>
       </c>
       <c r="J73" t="n">
-        <v>33.2895</v>
+        <v>33.4629</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
